--- a/resources/report/60/95/einvoices_template/SamWoon/MAU HOA DON GTGT_SAMWOON_CQT_V1.0.4.xlsx
+++ b/resources/report/60/95/einvoices_template/SamWoon/MAU HOA DON GTGT_SAMWOON_CQT_V1.0.4.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\GENUWIN\19. Package\75. GENUWIN SOLUTION\23.30 SAMWOON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\einvoices_template\SamWoon\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -631,7 +631,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="52" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1651,36 +1651,141 @@
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="17" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="21" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="42" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="42" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="18" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="18" borderId="17" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="18" borderId="21" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="17" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="21" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1698,111 +1803,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="42" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="42" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="27" fillId="18" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="27" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="18" borderId="17" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="18" borderId="21" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2233,20 +2233,20 @@
       <c r="C1" s="27"/>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
       <c r="R1" s="62"/>
       <c r="S1" s="53"/>
       <c r="T1" s="53"/>
@@ -2260,20 +2260,20 @@
       <c r="C2" s="51"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="110" t="s">
+      <c r="F2" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="110"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
       <c r="R2" s="3" t="s">
         <v>18</v>
       </c>
@@ -2289,20 +2289,20 @@
       <c r="A3" s="50"/>
       <c r="B3" s="51"/>
       <c r="C3" s="51"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
+      <c r="P3" s="130"/>
+      <c r="Q3" s="130"/>
       <c r="R3" s="3" t="s">
         <v>19</v>
       </c>
@@ -2320,20 +2320,20 @@
       <c r="C4" s="51"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="112" t="s">
+      <c r="F4" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
       <c r="R4" s="51"/>
       <c r="S4" s="51"/>
       <c r="T4" s="51"/>
@@ -2342,8 +2342,8 @@
       <c r="W4" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="114"/>
-      <c r="B5" s="115"/>
+      <c r="A5" s="121"/>
+      <c r="B5" s="122"/>
       <c r="C5" s="51"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -2352,13 +2352,13 @@
       </c>
       <c r="G5" s="70"/>
       <c r="H5" s="70"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
       <c r="P5" s="70"/>
       <c r="Q5" s="70"/>
       <c r="R5" s="51"/>
@@ -2369,23 +2369,23 @@
       <c r="W5" s="4"/>
     </row>
     <row r="6" spans="1:23" ht="0.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="114"/>
-      <c r="B6" s="115"/>
+      <c r="A6" s="121"/>
+      <c r="B6" s="122"/>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="64"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="117"/>
-      <c r="P6" s="117"/>
-      <c r="Q6" s="117"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="125"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="125"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="125"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="125"/>
+      <c r="P6" s="125"/>
+      <c r="Q6" s="125"/>
       <c r="R6" s="51"/>
       <c r="S6" s="51"/>
       <c r="T6" s="51"/>
@@ -2459,11 +2459,11 @@
       <c r="G9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
       <c r="M9" s="68"/>
       <c r="N9" s="68"/>
       <c r="O9" s="68"/>
@@ -2487,21 +2487,21 @@
       <c r="G10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="118"/>
-      <c r="O10" s="118"/>
-      <c r="P10" s="118"/>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="118"/>
-      <c r="S10" s="118"/>
-      <c r="T10" s="118"/>
-      <c r="U10" s="118"/>
-      <c r="V10" s="118"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="126"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="126"/>
+      <c r="O10" s="126"/>
+      <c r="P10" s="126"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
+      <c r="S10" s="126"/>
+      <c r="T10" s="126"/>
+      <c r="U10" s="126"/>
+      <c r="V10" s="126"/>
       <c r="W10" s="4"/>
     </row>
     <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
@@ -2516,21 +2516,21 @@
       <c r="G11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="119"/>
-      <c r="N11" s="119"/>
-      <c r="O11" s="119"/>
-      <c r="P11" s="119"/>
-      <c r="Q11" s="119"/>
-      <c r="R11" s="119"/>
-      <c r="S11" s="119"/>
-      <c r="T11" s="119"/>
-      <c r="U11" s="119"/>
-      <c r="V11" s="119"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
+      <c r="T11" s="127"/>
+      <c r="U11" s="127"/>
+      <c r="V11" s="127"/>
       <c r="W11" s="6"/>
     </row>
     <row r="12" spans="1:23" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2545,21 +2545,21 @@
       <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
-      <c r="L12" s="94"/>
-      <c r="M12" s="94"/>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="94"/>
-      <c r="T12" s="94"/>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="124"/>
+      <c r="R12" s="124"/>
+      <c r="S12" s="124"/>
+      <c r="T12" s="124"/>
+      <c r="U12" s="124"/>
+      <c r="V12" s="124"/>
       <c r="W12" s="6"/>
     </row>
     <row r="13" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2570,21 +2570,21 @@
       <c r="E13" s="64"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
-      <c r="S13" s="94"/>
-      <c r="T13" s="94"/>
-      <c r="U13" s="94"/>
-      <c r="V13" s="94"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="124"/>
+      <c r="N13" s="124"/>
+      <c r="O13" s="124"/>
+      <c r="P13" s="124"/>
+      <c r="Q13" s="124"/>
+      <c r="R13" s="124"/>
+      <c r="S13" s="124"/>
+      <c r="T13" s="124"/>
+      <c r="U13" s="124"/>
+      <c r="V13" s="124"/>
       <c r="W13" s="6"/>
     </row>
     <row r="14" spans="1:23" ht="0.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2649,19 +2649,19 @@
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="93"/>
-      <c r="T16" s="93"/>
-      <c r="U16" s="93"/>
-      <c r="V16" s="93"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="134"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="134"/>
+      <c r="P16" s="134"/>
+      <c r="Q16" s="134"/>
+      <c r="R16" s="134"/>
+      <c r="S16" s="134"/>
+      <c r="T16" s="134"/>
+      <c r="U16" s="134"/>
+      <c r="V16" s="134"/>
       <c r="W16" s="66"/>
     </row>
     <row r="17" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2673,22 +2673,22 @@
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="93"/>
-      <c r="S17" s="93"/>
-      <c r="T17" s="93"/>
-      <c r="U17" s="93"/>
-      <c r="V17" s="93"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="134"/>
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="134"/>
       <c r="W17" s="54"/>
     </row>
     <row r="18" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
@@ -2699,12 +2699,12 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="67"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="133"/>
       <c r="L18" s="40"/>
       <c r="M18" s="40"/>
       <c r="N18" s="8"/>
@@ -2724,25 +2724,25 @@
         <v>34</v>
       </c>
       <c r="C19" s="8"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="94"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="124"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="124"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="124"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="124"/>
+      <c r="S19" s="124"/>
+      <c r="T19" s="124"/>
+      <c r="U19" s="124"/>
+      <c r="V19" s="124"/>
       <c r="W19" s="54"/>
     </row>
     <row r="20" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -2757,19 +2757,19 @@
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
       <c r="I20" s="51"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138"/>
-      <c r="M20" s="138"/>
-      <c r="N20" s="138"/>
-      <c r="O20" s="138"/>
-      <c r="P20" s="138"/>
-      <c r="Q20" s="138"/>
-      <c r="R20" s="138"/>
-      <c r="S20" s="138"/>
-      <c r="T20" s="138"/>
-      <c r="U20" s="138"/>
-      <c r="V20" s="138"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="94"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="94"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+      <c r="T20" s="94"/>
+      <c r="U20" s="94"/>
+      <c r="V20" s="94"/>
       <c r="W20" s="4"/>
     </row>
     <row r="21" spans="1:23" ht="16.8" x14ac:dyDescent="0.25">
@@ -2780,10 +2780,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="138"/>
-      <c r="I21" s="138"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
       <c r="J21" s="64"/>
       <c r="K21" s="64"/>
       <c r="L21" s="11"/>
@@ -2796,9 +2796,9 @@
       <c r="Q21" s="51"/>
       <c r="R21" s="51"/>
       <c r="S21" s="51"/>
-      <c r="T21" s="138"/>
-      <c r="U21" s="138"/>
-      <c r="V21" s="138"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
       <c r="W21" s="4"/>
     </row>
     <row r="22" spans="1:23" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -2827,10 +2827,10 @@
       <c r="W22" s="4"/>
     </row>
     <row r="23" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="105"/>
+      <c r="B23" s="140"/>
       <c r="C23" s="12" t="s">
         <v>46</v>
       </c>
@@ -2864,10 +2864,10 @@
       <c r="W23" s="79"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="107"/>
+      <c r="B24" s="142"/>
       <c r="C24" s="82" t="s">
         <v>47</v>
       </c>
@@ -2938,84 +2938,84 @@
       <c r="W25" s="87"/>
     </row>
     <row r="26" spans="1:23" s="74" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="123"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="126"/>
-      <c r="I26" s="126"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="126"/>
-      <c r="L26" s="127"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="112"/>
       <c r="M26" s="72"/>
-      <c r="N26" s="130"/>
-      <c r="O26" s="131"/>
-      <c r="P26" s="132"/>
-      <c r="Q26" s="130"/>
-      <c r="R26" s="131"/>
-      <c r="S26" s="132"/>
-      <c r="T26" s="128"/>
-      <c r="U26" s="129"/>
-      <c r="V26" s="129"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="116"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="115"/>
+      <c r="R26" s="116"/>
+      <c r="S26" s="117"/>
+      <c r="T26" s="113"/>
+      <c r="U26" s="114"/>
+      <c r="V26" s="114"/>
       <c r="W26" s="73"/>
     </row>
     <row r="27" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26"/>
-      <c r="B27" s="135"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="135"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="135"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="97" t="s">
+      <c r="B27" s="120"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="N27" s="97"/>
-      <c r="O27" s="97"/>
-      <c r="P27" s="97"/>
-      <c r="Q27" s="97"/>
-      <c r="R27" s="97"/>
-      <c r="S27" s="98"/>
-      <c r="T27" s="99"/>
-      <c r="U27" s="100"/>
-      <c r="V27" s="100"/>
+      <c r="N27" s="99"/>
+      <c r="O27" s="99"/>
+      <c r="P27" s="99"/>
+      <c r="Q27" s="99"/>
+      <c r="R27" s="99"/>
+      <c r="S27" s="100"/>
+      <c r="T27" s="101"/>
+      <c r="U27" s="102"/>
+      <c r="V27" s="102"/>
       <c r="W27" s="41"/>
     </row>
     <row r="28" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
-      <c r="B28" s="101" t="s">
+      <c r="B28" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
       <c r="G28" s="57"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="101"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
       <c r="L28" s="57"/>
-      <c r="M28" s="97" t="s">
+      <c r="M28" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="N28" s="97"/>
-      <c r="O28" s="97"/>
-      <c r="P28" s="97"/>
-      <c r="Q28" s="97"/>
-      <c r="R28" s="97"/>
-      <c r="S28" s="98"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="100"/>
-      <c r="V28" s="100"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="99"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="99"/>
+      <c r="S28" s="100"/>
+      <c r="T28" s="101"/>
+      <c r="U28" s="102"/>
+      <c r="V28" s="102"/>
       <c r="W28" s="13"/>
     </row>
     <row r="29" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3031,18 +3031,18 @@
       <c r="J29" s="42"/>
       <c r="K29" s="42"/>
       <c r="L29" s="42"/>
-      <c r="M29" s="97" t="s">
+      <c r="M29" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="N29" s="97"/>
-      <c r="O29" s="97"/>
-      <c r="P29" s="97"/>
-      <c r="Q29" s="97"/>
-      <c r="R29" s="97"/>
-      <c r="S29" s="98"/>
-      <c r="T29" s="99"/>
-      <c r="U29" s="100"/>
-      <c r="V29" s="100"/>
+      <c r="N29" s="99"/>
+      <c r="O29" s="99"/>
+      <c r="P29" s="99"/>
+      <c r="Q29" s="99"/>
+      <c r="R29" s="99"/>
+      <c r="S29" s="100"/>
+      <c r="T29" s="101"/>
+      <c r="U29" s="102"/>
+      <c r="V29" s="102"/>
       <c r="W29" s="13"/>
     </row>
     <row r="30" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
@@ -3055,21 +3055,21 @@
       <c r="E30" s="65"/>
       <c r="F30" s="65"/>
       <c r="G30" s="65"/>
-      <c r="H30" s="102"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="102"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="102"/>
-      <c r="N30" s="102"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="102"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="102"/>
-      <c r="T30" s="102"/>
-      <c r="U30" s="102"/>
-      <c r="V30" s="102"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="137"/>
+      <c r="J30" s="137"/>
+      <c r="K30" s="137"/>
+      <c r="L30" s="137"/>
+      <c r="M30" s="137"/>
+      <c r="N30" s="137"/>
+      <c r="O30" s="137"/>
+      <c r="P30" s="137"/>
+      <c r="Q30" s="137"/>
+      <c r="R30" s="137"/>
+      <c r="S30" s="137"/>
+      <c r="T30" s="137"/>
+      <c r="U30" s="137"/>
+      <c r="V30" s="137"/>
       <c r="W30" s="14"/>
     </row>
     <row r="31" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -3080,108 +3080,108 @@
       <c r="E31" s="15"/>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="103"/>
-      <c r="K31" s="103"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="103"/>
-      <c r="N31" s="103"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="103"/>
-      <c r="Q31" s="103"/>
-      <c r="R31" s="103"/>
-      <c r="S31" s="103"/>
-      <c r="T31" s="103"/>
-      <c r="U31" s="103"/>
-      <c r="V31" s="103"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="138"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="138"/>
+      <c r="N31" s="138"/>
+      <c r="O31" s="138"/>
+      <c r="P31" s="138"/>
+      <c r="Q31" s="138"/>
+      <c r="R31" s="138"/>
+      <c r="S31" s="138"/>
+      <c r="T31" s="138"/>
+      <c r="U31" s="138"/>
+      <c r="V31" s="138"/>
       <c r="W31" s="17"/>
     </row>
     <row r="32" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A32" s="19"/>
-      <c r="B32" s="108" t="s">
+      <c r="B32" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="108"/>
-      <c r="D32" s="108"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="108"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="108"/>
-      <c r="I32" s="108"/>
-      <c r="J32" s="108"/>
-      <c r="K32" s="108"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="108"/>
-      <c r="N32" s="108"/>
-      <c r="O32" s="108" t="s">
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="105"/>
+      <c r="O32" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="P32" s="108"/>
-      <c r="Q32" s="108"/>
-      <c r="R32" s="108"/>
-      <c r="S32" s="108"/>
-      <c r="T32" s="108"/>
-      <c r="U32" s="108"/>
-      <c r="V32" s="108"/>
+      <c r="P32" s="105"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="105"/>
+      <c r="S32" s="105"/>
+      <c r="T32" s="105"/>
+      <c r="U32" s="105"/>
+      <c r="V32" s="105"/>
       <c r="W32" s="18"/>
     </row>
     <row r="33" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A33" s="48"/>
-      <c r="B33" s="95" t="s">
+      <c r="B33" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="95"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="95"/>
-      <c r="F33" s="95"/>
-      <c r="G33" s="95"/>
-      <c r="H33" s="95"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="96"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="96" t="s">
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135"/>
+      <c r="I33" s="136"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="136"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="P33" s="96"/>
-      <c r="Q33" s="96"/>
-      <c r="R33" s="96"/>
-      <c r="S33" s="96"/>
-      <c r="T33" s="96"/>
-      <c r="U33" s="96"/>
-      <c r="V33" s="96"/>
+      <c r="P33" s="136"/>
+      <c r="Q33" s="136"/>
+      <c r="R33" s="136"/>
+      <c r="S33" s="136"/>
+      <c r="T33" s="136"/>
+      <c r="U33" s="136"/>
+      <c r="V33" s="136"/>
       <c r="W33" s="20"/>
     </row>
     <row r="34" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A34" s="21"/>
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="122"/>
-      <c r="H34" s="122"/>
-      <c r="I34" s="122"/>
-      <c r="J34" s="122"/>
-      <c r="K34" s="122"/>
-      <c r="L34" s="122"/>
-      <c r="M34" s="122"/>
-      <c r="N34" s="122"/>
-      <c r="O34" s="122" t="s">
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="P34" s="122"/>
-      <c r="Q34" s="122"/>
-      <c r="R34" s="122"/>
-      <c r="S34" s="122"/>
-      <c r="T34" s="122"/>
-      <c r="U34" s="122"/>
-      <c r="V34" s="122"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="103"/>
+      <c r="R34" s="103"/>
+      <c r="S34" s="103"/>
+      <c r="T34" s="103"/>
+      <c r="U34" s="103"/>
+      <c r="V34" s="103"/>
       <c r="W34" s="22"/>
     </row>
     <row r="35" spans="1:23" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3229,11 +3229,11 @@
       </c>
       <c r="P36" s="29"/>
       <c r="Q36" s="29"/>
-      <c r="R36" s="133"/>
-      <c r="S36" s="133"/>
-      <c r="T36" s="133"/>
-      <c r="U36" s="133"/>
-      <c r="V36" s="134"/>
+      <c r="R36" s="118"/>
+      <c r="S36" s="118"/>
+      <c r="T36" s="118"/>
+      <c r="U36" s="118"/>
+      <c r="V36" s="119"/>
       <c r="W36" s="31"/>
     </row>
     <row r="37" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3251,16 +3251,16 @@
       <c r="L37" s="36"/>
       <c r="M37" s="36"/>
       <c r="N37" s="38"/>
-      <c r="O37" s="139" t="s">
+      <c r="O37" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="P37" s="140"/>
-      <c r="Q37" s="140"/>
-      <c r="R37" s="141"/>
-      <c r="S37" s="141"/>
-      <c r="T37" s="141"/>
-      <c r="U37" s="141"/>
-      <c r="V37" s="142"/>
+      <c r="P37" s="96"/>
+      <c r="Q37" s="96"/>
+      <c r="R37" s="97"/>
+      <c r="S37" s="97"/>
+      <c r="T37" s="97"/>
+      <c r="U37" s="97"/>
+      <c r="V37" s="98"/>
       <c r="W37" s="37"/>
     </row>
     <row r="38" spans="1:23" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -3283,11 +3283,11 @@
       </c>
       <c r="P38" s="32"/>
       <c r="Q38" s="47"/>
-      <c r="R38" s="120"/>
-      <c r="S38" s="120"/>
-      <c r="T38" s="120"/>
-      <c r="U38" s="120"/>
-      <c r="V38" s="121"/>
+      <c r="R38" s="106"/>
+      <c r="S38" s="106"/>
+      <c r="T38" s="106"/>
+      <c r="U38" s="106"/>
+      <c r="V38" s="107"/>
       <c r="W38" s="30"/>
     </row>
     <row r="39" spans="1:23" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3346,60 +3346,98 @@
     </row>
     <row r="41" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A41" s="58"/>
-      <c r="B41" s="136" t="s">
+      <c r="B41" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="136"/>
-      <c r="D41" s="136"/>
-      <c r="E41" s="136"/>
-      <c r="F41" s="136"/>
-      <c r="G41" s="136"/>
-      <c r="H41" s="136"/>
-      <c r="I41" s="136"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="136"/>
-      <c r="L41" s="136"/>
-      <c r="M41" s="136"/>
-      <c r="N41" s="136"/>
-      <c r="O41" s="136"/>
-      <c r="P41" s="136"/>
-      <c r="Q41" s="136"/>
-      <c r="R41" s="136"/>
-      <c r="S41" s="136"/>
-      <c r="T41" s="136"/>
-      <c r="U41" s="136"/>
-      <c r="V41" s="136"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+      <c r="M41" s="92"/>
+      <c r="N41" s="92"/>
+      <c r="O41" s="92"/>
+      <c r="P41" s="92"/>
+      <c r="Q41" s="92"/>
+      <c r="R41" s="92"/>
+      <c r="S41" s="92"/>
+      <c r="T41" s="92"/>
+      <c r="U41" s="92"/>
+      <c r="V41" s="92"/>
       <c r="W41" s="25"/>
     </row>
     <row r="42" spans="1:23" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A42" s="53"/>
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="137"/>
-      <c r="J42" s="137"/>
-      <c r="K42" s="137"/>
-      <c r="L42" s="137"/>
-      <c r="M42" s="137"/>
-      <c r="N42" s="137"/>
-      <c r="O42" s="137"/>
-      <c r="P42" s="137"/>
-      <c r="Q42" s="137"/>
-      <c r="R42" s="137"/>
-      <c r="S42" s="137"/>
-      <c r="T42" s="137"/>
-      <c r="U42" s="137"/>
-      <c r="V42" s="137"/>
+      <c r="C42" s="93"/>
+      <c r="D42" s="93"/>
+      <c r="E42" s="93"/>
+      <c r="F42" s="93"/>
+      <c r="G42" s="93"/>
+      <c r="H42" s="93"/>
+      <c r="I42" s="93"/>
+      <c r="J42" s="93"/>
+      <c r="K42" s="93"/>
+      <c r="L42" s="93"/>
+      <c r="M42" s="93"/>
+      <c r="N42" s="93"/>
+      <c r="O42" s="93"/>
+      <c r="P42" s="93"/>
+      <c r="Q42" s="93"/>
+      <c r="R42" s="93"/>
+      <c r="S42" s="93"/>
+      <c r="T42" s="93"/>
+      <c r="U42" s="93"/>
+      <c r="V42" s="93"/>
       <c r="W42" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="F18:K18"/>
+    <mergeCell ref="J16:V16"/>
+    <mergeCell ref="G17:V17"/>
+    <mergeCell ref="D19:V19"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="M29:S29"/>
+    <mergeCell ref="T29:V29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H30:V31"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="O32:V32"/>
+    <mergeCell ref="F1:Q1"/>
+    <mergeCell ref="F2:Q2"/>
+    <mergeCell ref="D3:Q3"/>
+    <mergeCell ref="F4:Q4"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="I5:O5"/>
+    <mergeCell ref="M12:V12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="M13:V13"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="F6:Q6"/>
+    <mergeCell ref="H10:V10"/>
+    <mergeCell ref="H11:V11"/>
+    <mergeCell ref="R38:V38"/>
+    <mergeCell ref="O34:V34"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="R36:V36"/>
+    <mergeCell ref="B27:L27"/>
     <mergeCell ref="B41:V41"/>
     <mergeCell ref="B42:V42"/>
     <mergeCell ref="J20:V20"/>
@@ -3416,44 +3454,6 @@
     <mergeCell ref="T28:V28"/>
     <mergeCell ref="B32:H32"/>
     <mergeCell ref="I32:N32"/>
-    <mergeCell ref="R38:V38"/>
-    <mergeCell ref="O34:V34"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="T26:V26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="R36:V36"/>
-    <mergeCell ref="B27:L27"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="M12:V12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="M13:V13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F6:Q6"/>
-    <mergeCell ref="H10:V10"/>
-    <mergeCell ref="H11:V11"/>
-    <mergeCell ref="F1:Q1"/>
-    <mergeCell ref="F2:Q2"/>
-    <mergeCell ref="D3:Q3"/>
-    <mergeCell ref="F4:Q4"/>
-    <mergeCell ref="H9:L9"/>
-    <mergeCell ref="F18:K18"/>
-    <mergeCell ref="J16:V16"/>
-    <mergeCell ref="G17:V17"/>
-    <mergeCell ref="D19:V19"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="M29:S29"/>
-    <mergeCell ref="T29:V29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H30:V31"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="O32:V32"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0.25" header="0.3" footer="0.05"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
